--- a/www/download/COUNTRY.SVN.rpO1.xlsx
+++ b/www/download/COUNTRY.SVN.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>Eslovênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.49387592371311</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.564464649528101</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.659121935129566</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.692520748907331</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.756629938465452</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.92447928619047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.01182824043428</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.00081058753711</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.863125422093881</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.802021157505804</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.802903282049704</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.796438372834759</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729659977856526</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.679902081177344</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.716948718120329</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>1.85808323376178</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.78321740842958</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>1.72289563699208</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1.71114332636595</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>1.85807579782732</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>1.74526736069736</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.64534876870346</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1.68324075472764</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>1.84411347660231</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>1.76489826928063</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.80914983082193</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>1.87607677513694</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>1.83819309742267</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>1.78581119228827</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1.74717743820562</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>3.97103950676177</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>3.83267346418554</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>3.71607620745723</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>3.69357384648705</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>3.85191978665288</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>3.88267229880413</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>3.62540280882129</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>3.75201732651748</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>3.98176110112108</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>3.87998192454752</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3.94910553457921</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>3.80154294862263</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>3.7149419948005</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>3.56264606613498</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>3.50730541266749</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1708.758</t>
+          <t>5.57670471907425</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1670.15</t>
+          <t>5.39168346654995</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1638.628</t>
+          <t>5.24508515217908</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1629.509</t>
+          <t>5.21930235831146</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1644.428</t>
+          <t>5.57723473312356</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1660.151</t>
+          <t>5.37348934653725</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1662.069</t>
+          <t>5.12415673621264</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1682.333</t>
+          <t>5.20626601087892</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1671.121</t>
+          <t>5.48028412299204</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1671.611</t>
+          <t>5.41439994293094</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1664.697</t>
+          <t>5.51702403816985</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1689.328</t>
+          <t>5.31018801787781</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1740.358</t>
+          <t>4.7812776353724</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1819.538</t>
+          <t>4.79932642108439</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1778.476</t>
+          <t>4.84096562264134</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1287.888</t>
+          <t>1465292506829.35</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1269.261</t>
+          <t>1268146454065.33</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1237.461</t>
+          <t>1226600674092.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1237.419</t>
+          <t>1415090546049.26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1255.282</t>
+          <t>1485109962450.43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1280.997</t>
+          <t>1574971890319</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1294.77</t>
+          <t>1703504689955.45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1311.437</t>
+          <t>1779481553373.65</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1313.919</t>
+          <t>2082468144021.47</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1319.254</t>
+          <t>2024860959421.96</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1322.093</t>
+          <t>1920924584155.76</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1343.542</t>
+          <t>1768659928617.31</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1387.787</t>
+          <t>1586841744778.26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1430.053</t>
+          <t>1383663134793.18</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1393.705</t>
+          <t>1172770643576.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>208492904238.922</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>183260683818.553</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>176979234656.172</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>203341649535.067</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>218387289421.533</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>227674835030.974</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>250996917689.696</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>269289337145.692</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>319996484686.958</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>307935406455.238</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>289384532487.733</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>267109202304.985</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>239698484100.151</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>211893693961.075</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>193991587842.345</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1240338748.29219</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1078524349.3032</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1073311443.20926</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1200236432.97303</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>1297170393.13128</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>1420854773.73817</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>1537343458.76909</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>62.09</t>
+          <t>1446423084.03569</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60.03</t>
+          <t>1386545505.38294</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>1163677574.19572</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>1044197414.97483</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>871319322.675844</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>629859080.152628</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>476480769.499866</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>484890467.904803</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>35538.3271567305</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>34362.5309734312</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>32650.9672537832</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>34136.9970773824</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>34000.5256505839</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>31341.9253539704</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>32238.4477431094</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>35633.834172735</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>43778.4560322476</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>51281.4373720044</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>54312.9880509822</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>57520.8010421065</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>68321.4610485979</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>80805.3946108564</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>75976.4534662208</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>65874.6900227172</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>64035.9872677196</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>60636.9505538962</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>63484.7729215065</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>62105.0745837921</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>58073.4998597681</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>59395.077585181</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>64868.7798367998</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>79764.0299222053</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>93217.6189851008</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>98989.9793495888</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>105724.151938372</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>126497.922202642</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>146955.876286152</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>129678.350489908</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>66.73</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>67.95</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>65.87</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>4600.07350075678</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>4509.21042852256</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>4316.10353506834</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>4747.61153442491</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>4803.44439850744</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>4146.60082110677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>4191.53133922894</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>4462.08020053235</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.36</t>
+          <t>5586.82484942675</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>6778.10119338425</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>7120.80529720394</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>7703.03613571858</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>8850.07892662694</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>10928.0606762985</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>7715.81201843587</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.49387592371311</t>
+          <t>281157.876179685</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.564464649528101</t>
+          <t>250714.729700204</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.659121935129566</t>
+          <t>248020.139154463</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.692520748907331</t>
+          <t>284967.43731099</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.756629938465452</t>
+          <t>301840.434627886</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.92447928619047</t>
+          <t>308316.994966408</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.01182824043428</t>
+          <t>336506.61315971</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00081058753711</t>
+          <t>356388.092150671</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.863125422093881</t>
+          <t>423095.006613521</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021157505804</t>
+          <t>405560.780967357</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.802903282049704</t>
+          <t>380593.848211656</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796438372834759</t>
+          <t>345848.091433576</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729659977856526</t>
+          <t>300709.417897342</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902081177344</t>
+          <t>258186.855303923</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948718120329</t>
+          <t>242330.152727513</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-104810325488.997</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-78743146234.4901</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-64607327779.5634</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-74419468301.5247</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-74007480102.9914</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-76497599004.3652</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-87493223598.4358</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-79469127962.8924</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-89546354317.3615</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-86485970890.5316</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-97626606095.741</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-83191088561.6202</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-65766581513.3972</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-74432702978.4479</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-68835155722.4717</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-95176137407.4573</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-71085892687.0789</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-56476464919.9426</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-63399823883.5059</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-62272484156.1438</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-65246633825.0794</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-72333207956.3292</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-64139644240.0759</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-68736606573.7951</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-74877014402.9635</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-83003212937.0028</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-71646879187.1089</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-55838775921.4427</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>-71397307460.9695</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-64863722809.8384</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-9634188081.53934</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-7657253547.41115</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-8130862859.62076</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-11019644418.0188</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-11734995946.8476</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-11250965179.2858</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-15160015642.1066</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>-15329483722.8165</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-20809747743.5664</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-11608956487.5681</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>-14623393158.7382</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>-11544209374.5113</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-9927805591.95449</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>-3035395517.47838</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>-3971432912.6333</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1260283.8930098</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1090479.42111516</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1050930.37844065</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1200986.20862039</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1312139.55712357</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1314033.50730679</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1395573.42616466</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1499015.34092315</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1829483.92301557</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1702836.45326019</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1608836.0576617</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1432696.69426976</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1218023.25792899</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1019774.81907609</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>937001.39763669</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1328030.5562757</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1191006.1052449</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1200125.25747813</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1397714.71135138</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1506952.44906501</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1562441.77372675</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1710350.75321091</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1817907.09270662</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2164660.0067851</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2113567.21045949</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2000701.64348282</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1829778.51871769</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1604133.39841384</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1381577.26355452</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1295534.37160551</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>185.81</t>
+          <t>9272.3561394543</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>178.32</t>
+          <t>9285.34225976318</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>172.29</t>
+          <t>9365.768802039</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>171.11</t>
+          <t>10013.910562401</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>185.81</t>
+          <t>9573.69797367611</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>174.53</t>
+          <t>9813.22345086639</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>164.53</t>
+          <t>10317.846404815</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>168.32</t>
+          <t>11657.1211508588</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>184.41</t>
+          <t>14287.0125469065</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>176.49</t>
+          <t>18044.2917899178</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>180.91</t>
+          <t>20166.8374977181</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>187.61</t>
+          <t>23576.8940889948</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>183.82</t>
+          <t>29219.0397060095</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>178.58</t>
+          <t>32166.3406084947</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>174.72</t>
+          <t>24932.8159572924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>397.1</t>
+          <t>427290847155.357</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>383.27</t>
+          <t>368183671475.004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>371.61</t>
+          <t>365932158694.672</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>369.36</t>
+          <t>431867375730.329</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>385.19</t>
+          <t>448514573569.283</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>388.27</t>
+          <t>503295658703.598</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>362.54</t>
+          <t>565165821380.113</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>375.2</t>
+          <t>596519711217.412</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>398.18</t>
+          <t>688607847581.071</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>707423843886.743</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>394.91</t>
+          <t>711167328243.15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>380.15</t>
+          <t>692453969024.747</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>371.49</t>
+          <t>618447854720.251</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>356.26</t>
+          <t>522001345630.419</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>350.73</t>
+          <t>409959615563.526</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>557.67</t>
+          <t>9797.41148269065</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>539.17</t>
+          <t>9722.74805747548</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>524.51</t>
+          <t>9752.39271097419</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>521.93</t>
+          <t>10389.181562587</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>557.72</t>
+          <t>10471.0286433887</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>537.35</t>
+          <t>10541.5333387254</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>512.42</t>
+          <t>10558.6099646328</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>520.63</t>
+          <t>11480.3334118506</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>548.03</t>
+          <t>14456.1382515723</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>541.44</t>
+          <t>18654.9436607727</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>551.7</t>
+          <t>20708.9772832165</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>531.02</t>
+          <t>24089.404044779</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>478.13</t>
+          <t>30342.3600938279</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>479.93</t>
+          <t>34397.0564148913</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>484.1</t>
+          <t>24863.4479545927</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1219263.526</t>
+          <t>341643437132.12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1071326.666</t>
+          <t>303675807038.13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1059225.752</t>
+          <t>314213185844.365</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1231389.456</t>
+          <t>371521059788.295</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1345924.031</t>
+          <t>410738790013.78</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1413548.885</t>
+          <t>459938665914.411</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1554553.193</t>
+          <t>489453765138.299</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1677619.202</t>
+          <t>508710580567.911</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1989826.912</t>
+          <t>606576859651.673</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1948899.189</t>
+          <t>643195832750.842</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1841271.732</t>
+          <t>631108117227.268</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1709305.901</t>
+          <t>623421486132.91</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1543595.008</t>
+          <t>575530279412.06</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1373608.629</t>
+          <t>481106515873.846</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1261624.849</t>
+          <t>340098242211.977</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>934564.781</t>
+          <t>-525.055343236346</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>797089.204</t>
+          <t>-437.405797712301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>749910.288</t>
+          <t>-386.623908935183</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>856976.92</t>
+          <t>-375.271000185987</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>949357.9</t>
+          <t>-897.330669712611</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>970340.159</t>
+          <t>-728.309887858981</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1040944.263</t>
+          <t>-240.763559817807</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1132666.485</t>
+          <t>176.787739008212</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1383680.769</t>
+          <t>-169.125704665741</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1292934.771</t>
+          <t>-610.651870854832</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1223278.496</t>
+          <t>-542.139785498375</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1106516.071</t>
+          <t>-512.509955784204</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>970898.519</t>
+          <t>-1123.32038781845</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>836928.174</t>
+          <t>-2230.71580639669</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>750093.981</t>
+          <t>69.3680026997011</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1465292.507</t>
+          <t>85647410023.2367</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1268146.454</t>
+          <t>64507864436.8737</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1226600.674</t>
+          <t>51718972850.3072</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1415090.546</t>
+          <t>60346315942.0347</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1485109.962</t>
+          <t>37775783555.5034</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1574971.89</t>
+          <t>43356992789.1864</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1703504.69</t>
+          <t>75712056241.814</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1779481.553</t>
+          <t>87809130649.501</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2082468.144</t>
+          <t>82030987929.3986</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2024860.959</t>
+          <t>64228011135.9014</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1920924.584</t>
+          <t>80059211015.8822</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1768659.929</t>
+          <t>69032482891.837</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1586841.745</t>
+          <t>42917575308.1915</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1383663.135</t>
+          <t>40894829756.5727</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1172770.644</t>
+          <t>69861373351.5486</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>9468.17638</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>9553.40543</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>9503.65261</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>10003.98798</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>10064.26296</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>9203.21878</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>9365.37753</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>10408.59163</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>13025.09187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>15081.76118</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>15889.79686</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>17210.51997</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>20880.94144</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>23843.3406</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>20616.80425</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>790501.549</t>
+          <t>-0.041061753482446</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>680503.63</t>
+          <t>-0.0232466507270213</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>660483.386</t>
+          <t>-0.00421681301572432</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>760921.708</t>
+          <t>-0.00316315231198634</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>813049.815</t>
+          <t>0.00318328148197952</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>850003.04</t>
+          <t>0.009974022444106</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>924627.918</t>
+          <t>0.0121147989031757</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>977507.99</t>
+          <t>0.0199044730849146</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1142961.811</t>
+          <t>0.0251690488199995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1113928.693</t>
+          <t>0.0201349470352987</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1053956.72</t>
+          <t>0.0230952996990488</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>962265.802</t>
+          <t>0.0270879158919468</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>857052.389</t>
+          <t>0.0358211088506305</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>760823.238</t>
+          <t>0.0219737183329742</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>687107.4</t>
+          <t>0.0322525832681607</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>11620.1369238212</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>11384.3056424847</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>10709.4891936987</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>11083.3810905755</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>11180.7760355203</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>10295.4488956846</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>10625.4286805587</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>11845.1108065973</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>14830.0951715441</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>17269.3779092422</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>18247.4300526506</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>19678.4004124698</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>23588.5602801829</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>27890.5342784981</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>26281.4710697563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>208492.904</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>183260.684</t>
+          <t>14513.5561779957</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>176979.235</t>
+          <t>13648.5087300115</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>203341.65</t>
+          <t>14067.2700511963</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>218387.289</t>
+          <t>14138.4792389739</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>227674.835</t>
+          <t>12828.319893295</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>250996.918</t>
+          <t>13125.6410110016</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>269289.337</t>
+          <t>14692.7626133391</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>319996.485</t>
+          <t>18237.6396378539</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>307935.406</t>
+          <t>21236.2686187478</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>289384.532</t>
+          <t>22383.7224061932</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>267109.202</t>
+          <t>24088.5110512577</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>239698.484</t>
+          <t>28899.233180043</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>211893.694</t>
+          <t>34279.4176577063</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>193991.588</t>
+          <t>32150.0842224023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>42389.9215887585</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>42892.9633015573</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>41831.5572499992</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>45361.851554707</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>46489.8323809797</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>43248.2268829437</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>44081.1831907078</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>48971.3232784494</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>62434.2065509712</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>75315.7892697419</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>81725.3394066407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>88550.1288689718</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>107022.898406523</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>134173.403031698</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>98881.1982173894</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1240.339</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1078.524</t>
+          <t>15003.2649727884</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1073.311</t>
+          <t>14922.9701872133</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1200.236</t>
+          <t>15173.4962760684</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1297.17</t>
+          <t>15701.9804444718</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1420.855</t>
+          <t>16350.3662923365</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1537.343</t>
+          <t>16979.3258268696</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1446.423</t>
+          <t>17620.7621463449</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1386.546</t>
+          <t>17819.490583779</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1163.678</t>
+          <t>18610.3620447041</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1044.197</t>
+          <t>19259.8288859295</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>871.319</t>
+          <t>20137.8783819463</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>629.859</t>
+          <t>21070.3153595469</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>476.481</t>
+          <t>22344.5842434324</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>484.89</t>
+          <t>21485.7949799498</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11620.1369238212</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11656.7466722342</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11612.5759383847</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11892.5620345832</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12250.8383044423</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12994.5453810855</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13546.5762940706</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14024.1579924517</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14282.7705288857</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14978.350651655</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15666.1699242002</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>16387.9639260992</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>17339.2450984101</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>18317.4158893551</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>17673.1445639795</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2859.46899033896</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3512.09269200432</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4139.70767998852</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4604.12508880365</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4951.43462102615</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4577.95960670504</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4725.56600899841</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5436.8285866609</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7158.23444214607</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>8294.58062125223</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>9008.27650380679</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>10101.6745787423</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>12683.757819957</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>13876.3492422936</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10904.9860975977</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>934564781145.307</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>797089204302.387</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>749910288283.136</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>856976920009.371</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>949357900230.486</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>970340159269.653</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1040944262841.96</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1132666484708.92</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1383680769106.91</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1292934770740.76</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1223278496443.07</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1106516070582.06</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>970898519127.776</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>836928174240.932</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>750093980844.509</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1219263525686.17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1071326665753.26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1059225751749.17</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1231389456129.99</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1345924031215.27</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1413548884899.46</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1554553192750.18</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1677619202362.45</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1989826912017.08</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1948899189092.59</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1841271731618.61</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1709305901045.32</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1543595008091.1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1373608628647.44</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1261624849202.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>790501548774.639</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>680503630317.789</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>660483386407.546</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>760921707862.806</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>813049814538.207</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>850003039943.819</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>924627918003.975</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>977507989912.665</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1142961810862.82</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1113928692967.48</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1053956720383.16</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>962265802088.864</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>857052389228.042</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>760823237838.726</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>687107399898.498</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>918099</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>899514</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>882596</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>881002</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>893143</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>904705</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>908909</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>922830</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>919233</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>922090</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>920313</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>934160</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>962261</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>994232.219132951</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>973825.841177403</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>741551</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>730953</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>713568</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>713561</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>723519</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>738444</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>745890</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>755607</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>756323</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>759283</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>760350</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>772331</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>797110</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>820699</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>800526</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1708757625.80647</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1670150120.2685</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1638627648.55927</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1629509098.6178</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1644428387.08447</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1660151050.6775</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1662068675.97344</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1682333193.89346</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1671120525.92652</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1671610829.04208</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1664696902.32574</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1689328102.08285</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1740358030.68536</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1819537674.08294</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1778476269.73853</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1287887658.44177</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1269260505.82646</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1237460870.20158</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1237419425.58602</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1255281960.24692</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1280996781.98652</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1294769820.60965</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1311436755.34495</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1313919474.72281</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1319253617.09501</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1322092727.88369</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1343541682.80064</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1387787215.2592</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1430053445.43154</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1393704986.53083</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.257023267552655</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.279413119243087</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.230621348589472</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.257362321072398</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.285823508591103</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.300466154223845</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.30899248679988</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.31293809402232</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.314209084368503</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.321657071696235</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.341631791924359</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.628636805898128</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.603415954512167</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.63837916359736</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.620910986397626</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.600341285626231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.594092410633173</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.590468665356388</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.592062285047216</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.58441641414411</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.58000538446106</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.566979901880087</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.114339926549217</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.117170926244746</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.130999487813169</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.121726692529977</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.113835205782666</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.105441435142982</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.100538847843732</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0949996209304649</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.101374501487387</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0983375438427051</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0913883061955541</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.153428418671205</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.163047805157799</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.134658971574206</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.148873839431078</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.169459064090797</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.179940913358341</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.186909815187493</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.198040398164625</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.202323456638045</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.209431689172736</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.223685859238385</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.679689624684062</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.66734478186268</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.679472906294703</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.678961289278051</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.666898397724071</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.666051242258056</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.665832069252872</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.663491474463731</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.658672057320843</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.651355114958407</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.643975098581195</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.166881956644733</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.16960741297952</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.185868122131091</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.172164871290872</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.163642538185132</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.154007844383604</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.147258115559636</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.138468127371644</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.139004486041112</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.139213195868857</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.132339042180419</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>40260.23086</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>40779.67183</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>39685.83759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41536.33577</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>41819.65685</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>39411.53714</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40018.74467</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44922.06561</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>56083.43718</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>65875.94685</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>70482.11437</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>78329.00244</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>97551.78466</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>112680.84917</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>95937.80408</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17824.08937</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18025.64887</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17788.21641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18671.39514</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19089.91386</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>17406.2795</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17851.20702</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20129.5912</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25395.87408</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>29530.84924</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>31391.99891</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>34190.18563</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>41582.991</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>48155.7669</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>43055.07032</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20935.3616311307</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22242.2910994064</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23780.3187472429</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25466.5858163651</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>27496.1382046508</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29446.0190245068</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>31307.6121063329</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33038.5226663467</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>34925.1672613311</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>36925.5782712133</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>38932.9585921994</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>41245.4571810376</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>44221.4509312072</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>49870.5902665899</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>38591.9125511486</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
